--- a/reports/compliance_report.xlsx
+++ b/reports/compliance_report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26 03:06:22</t>
+          <t>2026-01-26 03:10:21</t>
         </is>
       </c>
     </row>
